--- a/Nuevos DeepWins/Problem3_CheckerRotated/Res/Comparativa_9_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem3_CheckerRotated/Res/Comparativa_9_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.24827</v>
+        <v>0.24184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.559524</v>
+        <v>0.543413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30719</v>
+        <v>0.47451</v>
       </c>
       <c r="I2" t="n">
-        <v>0.396624</v>
+        <v>0.506629</v>
       </c>
       <c r="J2" t="n">
-        <v>0.252243</v>
+        <v>0.258981</v>
       </c>
       <c r="K2" t="n">
-        <v>0.495652</v>
+        <v>0.487047</v>
       </c>
       <c r="L2" t="n">
-        <v>0.28934</v>
+        <v>0.477157</v>
       </c>
       <c r="M2" t="n">
-        <v>0.365385</v>
+        <v>0.482051</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_7.txt</t>
+          <t>_2_9_1_1790731036_6.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>9</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,42 +682,42 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.242248</v>
+        <v>0.24827</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5334370000000001</v>
+        <v>0.559524</v>
       </c>
       <c r="H3" t="n">
-        <v>0.448366</v>
+        <v>0.30719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.487216</v>
+        <v>0.396624</v>
       </c>
       <c r="J3" t="n">
-        <v>0.258341</v>
+        <v>0.252243</v>
       </c>
       <c r="K3" t="n">
-        <v>0.475936</v>
+        <v>0.495652</v>
       </c>
       <c r="L3" t="n">
-        <v>0.451777</v>
+        <v>0.28934</v>
       </c>
       <c r="M3" t="n">
-        <v>0.463542</v>
+        <v>0.365385</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,23 +753,23 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_19.txt</t>
+          <t>_2_3_3_3_1_1790731086_7.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>9</v>
       </c>
       <c r="AA3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.242386</v>
+        <v>0.24795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.541284</v>
+        <v>0.554156</v>
       </c>
       <c r="H4" t="n">
-        <v>0.462745</v>
+        <v>0.287582</v>
       </c>
       <c r="I4" t="n">
-        <v>0.498943</v>
+        <v>0.378657</v>
       </c>
       <c r="J4" t="n">
-        <v>0.258864</v>
+        <v>0.252268</v>
       </c>
       <c r="K4" t="n">
-        <v>0.461538</v>
+        <v>0.472727</v>
       </c>
       <c r="L4" t="n">
-        <v>0.456853</v>
+        <v>0.263959</v>
       </c>
       <c r="M4" t="n">
-        <v>0.459184</v>
+        <v>0.338762</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_3.txt</t>
+          <t>_2_3_3_3_1_1790731086_11.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>9</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,42 +884,42 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.242244</v>
+        <v>0.248426</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.544882</v>
+        <v>0.561772</v>
       </c>
       <c r="H5" t="n">
-        <v>0.452288</v>
+        <v>0.315033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.494286</v>
+        <v>0.403685</v>
       </c>
       <c r="J5" t="n">
-        <v>0.259035</v>
+        <v>0.252621</v>
       </c>
       <c r="K5" t="n">
-        <v>0.465517</v>
+        <v>0.495652</v>
       </c>
       <c r="L5" t="n">
-        <v>0.411168</v>
+        <v>0.28934</v>
       </c>
       <c r="M5" t="n">
-        <v>0.436658</v>
+        <v>0.365385</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_5.txt</t>
+          <t>_2_3_3_3_1_1790731086_13.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>9</v>
       </c>
       <c r="AA5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.242172</v>
+        <v>0.247411</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.541667</v>
+        <v>0.538813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.458824</v>
+        <v>0.308497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.496815</v>
+        <v>0.392352</v>
       </c>
       <c r="J6" t="n">
-        <v>0.258683</v>
+        <v>0.251915</v>
       </c>
       <c r="K6" t="n">
-        <v>0.467391</v>
+        <v>0.475</v>
       </c>
       <c r="L6" t="n">
-        <v>0.436548</v>
+        <v>0.28934</v>
       </c>
       <c r="M6" t="n">
-        <v>0.451444</v>
+        <v>0.359621</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_7.txt</t>
+          <t>_2_3_3_3_1_1790731086_8.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>9</v>
       </c>
       <c r="AA6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,7 +1086,7 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.242191</v>
+        <v>0.242244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.542056</v>
+        <v>0.542453</v>
       </c>
       <c r="H7" t="n">
-        <v>0.454902</v>
+        <v>0.45098</v>
       </c>
       <c r="I7" t="n">
-        <v>0.49467</v>
+        <v>0.492505</v>
       </c>
       <c r="J7" t="n">
-        <v>0.257961</v>
+        <v>0.259349</v>
       </c>
       <c r="K7" t="n">
-        <v>0.481283</v>
+        <v>0.465909</v>
       </c>
       <c r="L7" t="n">
-        <v>0.456853</v>
+        <v>0.416244</v>
       </c>
       <c r="M7" t="n">
-        <v>0.46875</v>
+        <v>0.439678</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_0.txt</t>
+          <t>_2_9_1_1790731036_12.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1187,7 +1187,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.246651</v>
+        <v>0.248999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.520505</v>
+        <v>0.6875</v>
       </c>
       <c r="H8" t="n">
-        <v>0.215686</v>
+        <v>0.071895</v>
       </c>
       <c r="I8" t="n">
-        <v>0.304991</v>
+        <v>0.130178</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251325</v>
+        <v>0.251387</v>
       </c>
       <c r="K8" t="n">
-        <v>0.426966</v>
+        <v>0.666667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.192893</v>
+        <v>0.071066</v>
       </c>
       <c r="M8" t="n">
-        <v>0.265734</v>
+        <v>0.12844</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_9.txt</t>
+          <t>_2_3_3_3_1_1790731086_4.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1288,7 +1288,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.248667</v>
+        <v>0.248281</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.533181</v>
+        <v>0.509804</v>
       </c>
       <c r="H9" t="n">
-        <v>0.304575</v>
+        <v>0.237908</v>
       </c>
       <c r="I9" t="n">
-        <v>0.387687</v>
+        <v>0.324421</v>
       </c>
       <c r="J9" t="n">
-        <v>0.252139</v>
+        <v>0.25288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.47541</v>
+        <v>0.416667</v>
       </c>
       <c r="L9" t="n">
-        <v>0.294416</v>
+        <v>0.228426</v>
       </c>
       <c r="M9" t="n">
-        <v>0.363636</v>
+        <v>0.295082</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_15.txt</t>
+          <t>_2_3_3_3_1_1790731086_19.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.242185</v>
+        <v>0.242203</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.544324</v>
+        <v>0.539291</v>
       </c>
       <c r="H10" t="n">
         <v>0.457516</v>
       </c>
       <c r="I10" t="n">
-        <v>0.497159</v>
+        <v>0.49505</v>
       </c>
       <c r="J10" t="n">
-        <v>0.258828</v>
+        <v>0.258599</v>
       </c>
       <c r="K10" t="n">
-        <v>0.469945</v>
+        <v>0.461957</v>
       </c>
       <c r="L10" t="n">
-        <v>0.436548</v>
+        <v>0.431472</v>
       </c>
       <c r="M10" t="n">
-        <v>0.452632</v>
+        <v>0.446194</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_11.txt</t>
+          <t>_2_9_1_1790731036_9.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1490,7 +1490,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.248001</v>
+        <v>0.248662</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1507,16 +1507,16 @@
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.571429</v>
+        <v>0.545732</v>
       </c>
       <c r="H11" t="n">
-        <v>0.230065</v>
+        <v>0.233987</v>
       </c>
       <c r="I11" t="n">
-        <v>0.328052</v>
+        <v>0.327539</v>
       </c>
       <c r="J11" t="n">
-        <v>0.252935</v>
+        <v>0.252218</v>
       </c>
       <c r="K11" t="n">
         <v>0.536585</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_5.txt</t>
+          <t>_2_3_3_3_1_1790731086_6.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.246678</v>
+        <v>0.242196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E12" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.554945</v>
+        <v>0.544049</v>
       </c>
       <c r="H12" t="n">
-        <v>0.264052</v>
+        <v>0.460131</v>
       </c>
       <c r="I12" t="n">
-        <v>0.357839</v>
+        <v>0.498584</v>
       </c>
       <c r="J12" t="n">
-        <v>0.251102</v>
+        <v>0.259287</v>
       </c>
       <c r="K12" t="n">
-        <v>0.515464</v>
+        <v>0.47191</v>
       </c>
       <c r="L12" t="n">
-        <v>0.253807</v>
+        <v>0.426396</v>
       </c>
       <c r="M12" t="n">
-        <v>0.340136</v>
+        <v>0.448</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_0.txt</t>
+          <t>_2_9_1_1790731036_2.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>9</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.248379</v>
+        <v>0.248667</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1709,25 +1709,25 @@
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.55</v>
+        <v>0.533181</v>
       </c>
       <c r="H13" t="n">
-        <v>0.287582</v>
+        <v>0.304575</v>
       </c>
       <c r="I13" t="n">
-        <v>0.377682</v>
+        <v>0.387687</v>
       </c>
       <c r="J13" t="n">
-        <v>0.251367</v>
+        <v>0.252139</v>
       </c>
       <c r="K13" t="n">
-        <v>0.518182</v>
+        <v>0.47541</v>
       </c>
       <c r="L13" t="n">
-        <v>0.28934</v>
+        <v>0.294416</v>
       </c>
       <c r="M13" t="n">
-        <v>0.371335</v>
+        <v>0.363636</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_12.txt</t>
+          <t>_2_3_3_3_1_1790731086_15.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1793,42 +1793,42 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.246758</v>
+        <v>0.242301</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E14" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5771810000000001</v>
+        <v>0.537867</v>
       </c>
       <c r="H14" t="n">
-        <v>0.224837</v>
+        <v>0.454902</v>
       </c>
       <c r="I14" t="n">
-        <v>0.323612</v>
+        <v>0.492918</v>
       </c>
       <c r="J14" t="n">
-        <v>0.252398</v>
+        <v>0.258583</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474359</v>
+        <v>0.479167</v>
       </c>
       <c r="L14" t="n">
-        <v>0.187817</v>
+        <v>0.467005</v>
       </c>
       <c r="M14" t="n">
-        <v>0.269091</v>
+        <v>0.473008</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_3.txt</t>
+          <t>_2_9_1_1790731036_15.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>9</v>
       </c>
       <c r="AA14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1894,35 +1894,43 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.249341</v>
+        <v>0.242386</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0.541284</v>
+      </c>
       <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>0.462745</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.498943</v>
+      </c>
       <c r="J15" t="n">
-        <v>0.250579</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0.258864</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.461538</v>
+      </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>0.456853</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.459184</v>
+      </c>
       <c r="N15" t="n">
         <v>0.2</v>
       </c>
@@ -1957,23 +1965,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_1.txt</t>
+          <t>_2_9_1_1790731036_3.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>9</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1987,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.248999</v>
+        <v>0.248469</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2004,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6875</v>
+        <v>0.567237</v>
       </c>
       <c r="H16" t="n">
-        <v>0.071895</v>
+        <v>0.303268</v>
       </c>
       <c r="I16" t="n">
-        <v>0.130178</v>
+        <v>0.39523</v>
       </c>
       <c r="J16" t="n">
-        <v>0.251387</v>
+        <v>0.252299</v>
       </c>
       <c r="K16" t="n">
-        <v>0.666667</v>
+        <v>0.478632</v>
       </c>
       <c r="L16" t="n">
-        <v>0.071066</v>
+        <v>0.284264</v>
       </c>
       <c r="M16" t="n">
-        <v>0.12844</v>
+        <v>0.356688</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2058,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_4.txt</t>
+          <t>_2_3_3_3_1_1790731086_17.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2088,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.242342</v>
+        <v>0.241925</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2105,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5412979999999999</v>
+        <v>0.546407</v>
       </c>
       <c r="H17" t="n">
-        <v>0.479739</v>
+        <v>0.477124</v>
       </c>
       <c r="I17" t="n">
-        <v>0.508663</v>
+        <v>0.509421</v>
       </c>
       <c r="J17" t="n">
-        <v>0.258621</v>
+        <v>0.259101</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448649</v>
+        <v>0.482051</v>
       </c>
       <c r="L17" t="n">
-        <v>0.42132</v>
+        <v>0.477157</v>
       </c>
       <c r="M17" t="n">
-        <v>0.434555</v>
+        <v>0.479592</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2159,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_1.txt</t>
+          <t>_2_9_1_1790731036_8.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2189,42 +2197,42 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.242136</v>
+        <v>0.246678</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F18" t="n">
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.537242</v>
+        <v>0.554945</v>
       </c>
       <c r="H18" t="n">
-        <v>0.443137</v>
+        <v>0.264052</v>
       </c>
       <c r="I18" t="n">
-        <v>0.485673</v>
+        <v>0.357839</v>
       </c>
       <c r="J18" t="n">
-        <v>0.25783</v>
+        <v>0.251102</v>
       </c>
       <c r="K18" t="n">
-        <v>0.489247</v>
+        <v>0.515464</v>
       </c>
       <c r="L18" t="n">
-        <v>0.461929</v>
+        <v>0.253807</v>
       </c>
       <c r="M18" t="n">
-        <v>0.475196</v>
+        <v>0.340136</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2260,23 +2268,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_18.txt</t>
+          <t>_2_3_3_3_1_1790731086_0.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>9</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2290,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.241925</v>
+        <v>0.242172</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2307,25 +2315,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.546407</v>
+        <v>0.541667</v>
       </c>
       <c r="H19" t="n">
-        <v>0.477124</v>
+        <v>0.458824</v>
       </c>
       <c r="I19" t="n">
-        <v>0.509421</v>
+        <v>0.496815</v>
       </c>
       <c r="J19" t="n">
-        <v>0.259101</v>
+        <v>0.258683</v>
       </c>
       <c r="K19" t="n">
-        <v>0.482051</v>
+        <v>0.467391</v>
       </c>
       <c r="L19" t="n">
-        <v>0.477157</v>
+        <v>0.436548</v>
       </c>
       <c r="M19" t="n">
-        <v>0.479592</v>
+        <v>0.451444</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2361,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_8.txt</t>
+          <t>_2_9_1_1790731036_7.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2391,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.248469</v>
+        <v>0.246758</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2408,25 +2416,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.567237</v>
+        <v>0.5771810000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.303268</v>
+        <v>0.224837</v>
       </c>
       <c r="I20" t="n">
-        <v>0.39523</v>
+        <v>0.323612</v>
       </c>
       <c r="J20" t="n">
-        <v>0.252299</v>
+        <v>0.252398</v>
       </c>
       <c r="K20" t="n">
-        <v>0.478632</v>
+        <v>0.474359</v>
       </c>
       <c r="L20" t="n">
-        <v>0.284264</v>
+        <v>0.187817</v>
       </c>
       <c r="M20" t="n">
-        <v>0.356688</v>
+        <v>0.269091</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2462,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_17.txt</t>
+          <t>_2_3_3_3_1_1790731086_3.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2492,42 +2500,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.248281</v>
+        <v>0.24218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E21" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.509804</v>
+        <v>0.541864</v>
       </c>
       <c r="H21" t="n">
-        <v>0.237908</v>
+        <v>0.448366</v>
       </c>
       <c r="I21" t="n">
-        <v>0.324421</v>
+        <v>0.490701</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25288</v>
+        <v>0.258053</v>
       </c>
       <c r="K21" t="n">
-        <v>0.416667</v>
+        <v>0.465608</v>
       </c>
       <c r="L21" t="n">
-        <v>0.228426</v>
+        <v>0.446701</v>
       </c>
       <c r="M21" t="n">
-        <v>0.295082</v>
+        <v>0.455959</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2563,23 +2571,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_19.txt</t>
+          <t>_2_9_1_1790731036_17.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2593,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.24795</v>
+        <v>0.242136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E22" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.554156</v>
+        <v>0.537242</v>
       </c>
       <c r="H22" t="n">
-        <v>0.287582</v>
+        <v>0.443137</v>
       </c>
       <c r="I22" t="n">
-        <v>0.378657</v>
+        <v>0.485673</v>
       </c>
       <c r="J22" t="n">
-        <v>0.252268</v>
+        <v>0.25783</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472727</v>
+        <v>0.489247</v>
       </c>
       <c r="L22" t="n">
-        <v>0.263959</v>
+        <v>0.461929</v>
       </c>
       <c r="M22" t="n">
-        <v>0.338762</v>
+        <v>0.475196</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2664,23 +2672,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_11.txt</t>
+          <t>_2_9_1_1790731036_18.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>9</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2694,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.248426</v>
+        <v>0.242173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E23" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.561772</v>
+        <v>0.541791</v>
       </c>
       <c r="H23" t="n">
-        <v>0.315033</v>
+        <v>0.47451</v>
       </c>
       <c r="I23" t="n">
-        <v>0.403685</v>
+        <v>0.505923</v>
       </c>
       <c r="J23" t="n">
-        <v>0.252621</v>
+        <v>0.257702</v>
       </c>
       <c r="K23" t="n">
-        <v>0.495652</v>
+        <v>0.473958</v>
       </c>
       <c r="L23" t="n">
-        <v>0.28934</v>
+        <v>0.461929</v>
       </c>
       <c r="M23" t="n">
-        <v>0.365385</v>
+        <v>0.467866</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2765,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_13.txt</t>
+          <t>_2_9_1_1790731036_13.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>9</v>
       </c>
       <c r="AA23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2795,7 +2803,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.247871</v>
+        <v>0.246651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2812,25 +2820,25 @@
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.567282</v>
+        <v>0.520505</v>
       </c>
       <c r="H24" t="n">
-        <v>0.281046</v>
+        <v>0.215686</v>
       </c>
       <c r="I24" t="n">
-        <v>0.375874</v>
+        <v>0.304991</v>
       </c>
       <c r="J24" t="n">
-        <v>0.252226</v>
+        <v>0.251325</v>
       </c>
       <c r="K24" t="n">
-        <v>0.495413</v>
+        <v>0.426966</v>
       </c>
       <c r="L24" t="n">
-        <v>0.274112</v>
+        <v>0.192893</v>
       </c>
       <c r="M24" t="n">
-        <v>0.352941</v>
+        <v>0.265734</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2866,7 +2874,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_2.txt</t>
+          <t>_2_3_3_3_1_1790731086_9.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2896,7 +2904,7 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.24184</v>
+        <v>0.242003</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2913,25 +2921,25 @@
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.543413</v>
+        <v>0.529061</v>
       </c>
       <c r="H25" t="n">
-        <v>0.47451</v>
+        <v>0.464052</v>
       </c>
       <c r="I25" t="n">
-        <v>0.506629</v>
+        <v>0.494429</v>
       </c>
       <c r="J25" t="n">
-        <v>0.258981</v>
+        <v>0.257222</v>
       </c>
       <c r="K25" t="n">
-        <v>0.487047</v>
+        <v>0.472081</v>
       </c>
       <c r="L25" t="n">
-        <v>0.477157</v>
+        <v>0.472081</v>
       </c>
       <c r="M25" t="n">
-        <v>0.482051</v>
+        <v>0.472081</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2967,7 +2975,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_6.txt</t>
+          <t>_2_9_1_1790731036_14.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -2997,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.24902</v>
+        <v>0.24212</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E26" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.503563</v>
+        <v>0.534712</v>
       </c>
       <c r="H26" t="n">
-        <v>0.277124</v>
+        <v>0.473203</v>
       </c>
       <c r="I26" t="n">
-        <v>0.357504</v>
+        <v>0.502081</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2521</v>
+        <v>0.258526</v>
       </c>
       <c r="K26" t="n">
-        <v>0.429752</v>
+        <v>0.469072</v>
       </c>
       <c r="L26" t="n">
-        <v>0.263959</v>
+        <v>0.461929</v>
       </c>
       <c r="M26" t="n">
-        <v>0.327044</v>
+        <v>0.465473</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3068,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_14.txt</t>
+          <t>_2_9_1_1790731036_16.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>9</v>
       </c>
       <c r="AA26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3098,42 +3106,42 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.24846</v>
+        <v>0.242242</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E27" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.560976</v>
+        <v>0.546154</v>
       </c>
       <c r="H27" t="n">
-        <v>0.300654</v>
+        <v>0.464052</v>
       </c>
       <c r="I27" t="n">
-        <v>0.391489</v>
+        <v>0.501767</v>
       </c>
       <c r="J27" t="n">
-        <v>0.252198</v>
+        <v>0.259495</v>
       </c>
       <c r="K27" t="n">
-        <v>0.474576</v>
+        <v>0.467391</v>
       </c>
       <c r="L27" t="n">
-        <v>0.284264</v>
+        <v>0.436548</v>
       </c>
       <c r="M27" t="n">
-        <v>0.355556</v>
+        <v>0.451444</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3169,23 +3177,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_10.txt</t>
+          <t>_2_9_1_1790731036_10.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>9</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3199,42 +3207,42 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.242244</v>
+        <v>0.248724</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F28" t="n">
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.542453</v>
+        <v>0.5418500000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.45098</v>
+        <v>0.321569</v>
       </c>
       <c r="I28" t="n">
-        <v>0.492505</v>
+        <v>0.40361</v>
       </c>
       <c r="J28" t="n">
-        <v>0.259349</v>
+        <v>0.252578</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465909</v>
+        <v>0.488189</v>
       </c>
       <c r="L28" t="n">
-        <v>0.416244</v>
+        <v>0.314721</v>
       </c>
       <c r="M28" t="n">
-        <v>0.439678</v>
+        <v>0.382716</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3270,23 +3278,23 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_12.txt</t>
+          <t>_2_3_3_3_1_1790731086_16.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z28" t="n">
         <v>9</v>
       </c>
       <c r="AA28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3300,42 +3308,42 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.24212</v>
+        <v>0.248379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.534712</v>
+        <v>0.55</v>
       </c>
       <c r="H29" t="n">
-        <v>0.473203</v>
+        <v>0.287582</v>
       </c>
       <c r="I29" t="n">
-        <v>0.502081</v>
+        <v>0.377682</v>
       </c>
       <c r="J29" t="n">
-        <v>0.258526</v>
+        <v>0.251367</v>
       </c>
       <c r="K29" t="n">
-        <v>0.469072</v>
+        <v>0.518182</v>
       </c>
       <c r="L29" t="n">
-        <v>0.461929</v>
+        <v>0.28934</v>
       </c>
       <c r="M29" t="n">
-        <v>0.465473</v>
+        <v>0.371335</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3371,23 +3379,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_16.txt</t>
+          <t>_2_3_3_3_1_1790731086_12.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>9</v>
       </c>
       <c r="AA29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3401,42 +3409,42 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.248662</v>
+        <v>0.242248</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E30" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.545732</v>
+        <v>0.5334370000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.233987</v>
+        <v>0.448366</v>
       </c>
       <c r="I30" t="n">
-        <v>0.327539</v>
+        <v>0.487216</v>
       </c>
       <c r="J30" t="n">
-        <v>0.252218</v>
+        <v>0.258341</v>
       </c>
       <c r="K30" t="n">
-        <v>0.536585</v>
+        <v>0.475936</v>
       </c>
       <c r="L30" t="n">
-        <v>0.22335</v>
+        <v>0.451777</v>
       </c>
       <c r="M30" t="n">
-        <v>0.315412</v>
+        <v>0.463542</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3472,23 +3480,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_6.txt</t>
+          <t>_2_9_1_1790731036_19.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>9</v>
       </c>
       <c r="AA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3502,7 +3510,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.248724</v>
+        <v>0.248001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3519,25 +3527,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5418500000000001</v>
+        <v>0.571429</v>
       </c>
       <c r="H31" t="n">
-        <v>0.321569</v>
+        <v>0.230065</v>
       </c>
       <c r="I31" t="n">
-        <v>0.40361</v>
+        <v>0.328052</v>
       </c>
       <c r="J31" t="n">
-        <v>0.252578</v>
+        <v>0.252935</v>
       </c>
       <c r="K31" t="n">
-        <v>0.488189</v>
+        <v>0.536585</v>
       </c>
       <c r="L31" t="n">
-        <v>0.314721</v>
+        <v>0.22335</v>
       </c>
       <c r="M31" t="n">
-        <v>0.382716</v>
+        <v>0.315412</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3573,7 +3581,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_16.txt</t>
+          <t>_2_3_3_3_1_1790731086_5.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3603,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.242301</v>
+        <v>0.248857</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.537867</v>
+        <v>0.546667</v>
       </c>
       <c r="H32" t="n">
-        <v>0.454902</v>
+        <v>0.267974</v>
       </c>
       <c r="I32" t="n">
-        <v>0.492918</v>
+        <v>0.359649</v>
       </c>
       <c r="J32" t="n">
-        <v>0.258583</v>
+        <v>0.252101</v>
       </c>
       <c r="K32" t="n">
-        <v>0.479167</v>
+        <v>0.422018</v>
       </c>
       <c r="L32" t="n">
-        <v>0.467005</v>
+        <v>0.233503</v>
       </c>
       <c r="M32" t="n">
-        <v>0.473008</v>
+        <v>0.300654</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3674,23 +3682,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_15.txt</t>
+          <t>_2_3_3_3_1_1790731086_18.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>9</v>
       </c>
       <c r="AA32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3704,7 +3712,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.242203</v>
+        <v>0.242191</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3721,25 +3729,25 @@
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.539291</v>
+        <v>0.542056</v>
       </c>
       <c r="H33" t="n">
-        <v>0.457516</v>
+        <v>0.454902</v>
       </c>
       <c r="I33" t="n">
-        <v>0.49505</v>
+        <v>0.49467</v>
       </c>
       <c r="J33" t="n">
-        <v>0.258599</v>
+        <v>0.257961</v>
       </c>
       <c r="K33" t="n">
-        <v>0.461957</v>
+        <v>0.481283</v>
       </c>
       <c r="L33" t="n">
-        <v>0.431472</v>
+        <v>0.456853</v>
       </c>
       <c r="M33" t="n">
-        <v>0.446194</v>
+        <v>0.46875</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3775,7 +3783,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_9.txt</t>
+          <t>_2_9_1_1790731036_0.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3805,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.242173</v>
+        <v>0.242227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3822,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.541791</v>
+        <v>0.539062</v>
       </c>
       <c r="H34" t="n">
-        <v>0.47451</v>
+        <v>0.45098</v>
       </c>
       <c r="I34" t="n">
-        <v>0.505923</v>
+        <v>0.491103</v>
       </c>
       <c r="J34" t="n">
-        <v>0.257702</v>
+        <v>0.25885</v>
       </c>
       <c r="K34" t="n">
-        <v>0.473958</v>
+        <v>0.47486</v>
       </c>
       <c r="L34" t="n">
-        <v>0.461929</v>
+        <v>0.431472</v>
       </c>
       <c r="M34" t="n">
-        <v>0.467866</v>
+        <v>0.452128</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3876,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_13.txt</t>
+          <t>_2_9_1_1790731036_4.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3906,7 +3914,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.247411</v>
+        <v>0.247871</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3923,25 +3931,25 @@
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.538813</v>
+        <v>0.567282</v>
       </c>
       <c r="H35" t="n">
-        <v>0.308497</v>
+        <v>0.281046</v>
       </c>
       <c r="I35" t="n">
-        <v>0.392352</v>
+        <v>0.375874</v>
       </c>
       <c r="J35" t="n">
-        <v>0.251915</v>
+        <v>0.252226</v>
       </c>
       <c r="K35" t="n">
-        <v>0.475</v>
+        <v>0.495413</v>
       </c>
       <c r="L35" t="n">
-        <v>0.28934</v>
+        <v>0.274112</v>
       </c>
       <c r="M35" t="n">
-        <v>0.359621</v>
+        <v>0.352941</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3977,7 +3985,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_8.txt</t>
+          <t>_2_3_3_3_1_1790731086_2.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4007,42 +4015,42 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.242003</v>
+        <v>0.24846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F36" t="n">
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.529061</v>
+        <v>0.560976</v>
       </c>
       <c r="H36" t="n">
-        <v>0.464052</v>
+        <v>0.300654</v>
       </c>
       <c r="I36" t="n">
-        <v>0.494429</v>
+        <v>0.391489</v>
       </c>
       <c r="J36" t="n">
-        <v>0.257222</v>
+        <v>0.252198</v>
       </c>
       <c r="K36" t="n">
-        <v>0.472081</v>
+        <v>0.474576</v>
       </c>
       <c r="L36" t="n">
-        <v>0.472081</v>
+        <v>0.284264</v>
       </c>
       <c r="M36" t="n">
-        <v>0.472081</v>
+        <v>0.355556</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4078,23 +4086,23 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_14.txt</t>
+          <t>_2_3_3_3_1_1790731086_10.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z36" t="n">
         <v>9</v>
       </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4108,43 +4116,35 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.242227</v>
+        <v>0.249341</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F37" t="n">
         <v>200000</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.539062</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.45098</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.491103</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0.25885</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.47486</v>
-      </c>
+        <v>0.250579</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>0.431472</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.452128</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>0.2</v>
       </c>
@@ -4179,23 +4179,23 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_4.txt</t>
+          <t>_2_3_3_3_1_1790731086_1.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z37" t="n">
         <v>9</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4209,7 +4209,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.24218</v>
+        <v>0.242342</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4226,25 +4226,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.541864</v>
+        <v>0.5412979999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.448366</v>
+        <v>0.479739</v>
       </c>
       <c r="I38" t="n">
-        <v>0.490701</v>
+        <v>0.508663</v>
       </c>
       <c r="J38" t="n">
-        <v>0.258053</v>
+        <v>0.258621</v>
       </c>
       <c r="K38" t="n">
-        <v>0.465608</v>
+        <v>0.448649</v>
       </c>
       <c r="L38" t="n">
-        <v>0.446701</v>
+        <v>0.42132</v>
       </c>
       <c r="M38" t="n">
-        <v>0.455959</v>
+        <v>0.434555</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_17.txt</t>
+          <t>_2_9_1_1790731036_1.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4310,7 +4310,7 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.242242</v>
+        <v>0.242244</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4327,25 +4327,25 @@
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.546154</v>
+        <v>0.544882</v>
       </c>
       <c r="H39" t="n">
-        <v>0.464052</v>
+        <v>0.452288</v>
       </c>
       <c r="I39" t="n">
-        <v>0.501767</v>
+        <v>0.494286</v>
       </c>
       <c r="J39" t="n">
-        <v>0.259495</v>
+        <v>0.259035</v>
       </c>
       <c r="K39" t="n">
-        <v>0.467391</v>
+        <v>0.465517</v>
       </c>
       <c r="L39" t="n">
-        <v>0.436548</v>
+        <v>0.411168</v>
       </c>
       <c r="M39" t="n">
-        <v>0.451444</v>
+        <v>0.436658</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_10.txt</t>
+          <t>_2_9_1_1790731036_5.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4411,42 +4411,42 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.248857</v>
+        <v>0.242185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_</t>
+          <t>_2_9_1_</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1790731086</v>
+        <v>1790731036</v>
       </c>
       <c r="E40" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="F40" t="n">
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.546667</v>
+        <v>0.544324</v>
       </c>
       <c r="H40" t="n">
-        <v>0.267974</v>
+        <v>0.457516</v>
       </c>
       <c r="I40" t="n">
-        <v>0.359649</v>
+        <v>0.497159</v>
       </c>
       <c r="J40" t="n">
-        <v>0.252101</v>
+        <v>0.258828</v>
       </c>
       <c r="K40" t="n">
-        <v>0.422018</v>
+        <v>0.469945</v>
       </c>
       <c r="L40" t="n">
-        <v>0.233503</v>
+        <v>0.436548</v>
       </c>
       <c r="M40" t="n">
-        <v>0.300654</v>
+        <v>0.452632</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4482,23 +4482,23 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_3_3_3_1_1790731086_18.txt</t>
+          <t>_2_9_1_1790731036_11.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>[3, 3, 3]</t>
+          <t>[9]</t>
         </is>
       </c>
       <c r="Z40" t="n">
         <v>9</v>
       </c>
       <c r="AA40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4512,42 +4512,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.242196</v>
+        <v>0.24902</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_9_1_</t>
+          <t>_2_3_3_3_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790731036</v>
+        <v>1790731086</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.544049</v>
+        <v>0.503563</v>
       </c>
       <c r="H41" t="n">
-        <v>0.460131</v>
+        <v>0.277124</v>
       </c>
       <c r="I41" t="n">
-        <v>0.498584</v>
+        <v>0.357504</v>
       </c>
       <c r="J41" t="n">
-        <v>0.259287</v>
+        <v>0.2521</v>
       </c>
       <c r="K41" t="n">
-        <v>0.47191</v>
+        <v>0.429752</v>
       </c>
       <c r="L41" t="n">
-        <v>0.426396</v>
+        <v>0.263959</v>
       </c>
       <c r="M41" t="n">
-        <v>0.448</v>
+        <v>0.327044</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4583,23 +4583,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_9_1_1790731036_2.txt</t>
+          <t>_2_3_3_3_1_1790731086_14.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[3, 3, 3]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>9</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4674,7 +4674,7 @@
         <v>0.3246857894736842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05846004962230279</v>
+        <v>0.05846004962230281</v>
       </c>
       <c r="D2" t="n">
         <v>0.382716</v>
